--- a/diseases/d178/2000-2004.xlsx
+++ b/diseases/d178/2000-2004.xlsx
@@ -2348,6 +2348,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO10" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2496,6 +2501,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO11" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2644,6 +2654,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO12" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2792,6 +2807,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO13" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2940,6 +2960,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO14" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3088,6 +3113,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO15" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3236,6 +3266,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO16" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3384,6 +3419,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO17" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3532,6 +3572,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO18" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3680,6 +3725,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO19" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4221,6 +4271,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO22" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4369,6 +4424,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO23" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4517,6 +4577,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO24" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4665,6 +4730,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO25" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4813,6 +4883,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO26" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4961,6 +5036,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO27" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5109,6 +5189,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO28" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5257,6 +5342,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO29" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5405,6 +5495,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO30" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5553,6 +5648,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO31" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5701,6 +5801,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO32" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5847,6 +5952,11 @@
       <c r="S33" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">

--- a/diseases/d178/2000-2004.xlsx
+++ b/diseases/d178/2000-2004.xlsx
@@ -2343,11 +2343,6 @@
       <c r="R10" t="n">
         <v>0.02647355736154732</v>
       </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2360,23 +2355,13 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr"/>
       <c r="AT10" t="n">
         <v>0</v>
       </c>
-      <c r="AU10" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV10" t="inlineStr">
         <is>
           <t>nidss_open_data</t>
@@ -2496,11 +2481,6 @@
       <c r="R11" t="n">
         <v>0.0352980764820631</v>
       </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2513,23 +2493,13 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr"/>
       <c r="AT11" t="n">
         <v>0</v>
       </c>
-      <c r="AU11" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV11" t="inlineStr">
         <is>
           <t>nidss_open_data</t>
@@ -2649,11 +2619,6 @@
       <c r="R12" t="n">
         <v>0.04853485516283675</v>
       </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2666,23 +2631,13 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR12" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr"/>
       <c r="AT12" t="n">
         <v>0</v>
       </c>
-      <c r="AU12" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV12" t="inlineStr">
         <is>
           <t>nidss_open_data</t>
@@ -2802,11 +2757,6 @@
       <c r="R13" t="n">
         <v>0.02647355736154732</v>
       </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2819,23 +2769,13 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR13" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr"/>
       <c r="AT13" t="n">
         <v>0</v>
       </c>
-      <c r="AU13" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV13" t="inlineStr">
         <is>
           <t>nidss_open_data</t>
@@ -2955,11 +2895,6 @@
       <c r="R14" t="n">
         <v>0.02647355736154732</v>
       </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2972,23 +2907,13 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR14" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr"/>
       <c r="AT14" t="n">
         <v>0</v>
       </c>
-      <c r="AU14" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV14" t="inlineStr">
         <is>
           <t>nidss_open_data</t>
@@ -3108,11 +3033,6 @@
       <c r="R15" t="n">
         <v>0.02206129780128943</v>
       </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3125,23 +3045,13 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR15" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr"/>
       <c r="AT15" t="n">
         <v>0</v>
       </c>
-      <c r="AU15" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV15" t="inlineStr">
         <is>
           <t>nidss_open_data</t>
@@ -3261,11 +3171,6 @@
       <c r="R16" t="n">
         <v>0.02647355736154732</v>
       </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3278,23 +3183,13 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR16" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr"/>
       <c r="AT16" t="n">
         <v>0</v>
       </c>
-      <c r="AU16" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV16" t="inlineStr">
         <is>
           <t>nidss_open_data</t>
@@ -3414,11 +3309,6 @@
       <c r="R17" t="n">
         <v>0.03088581692180521</v>
       </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3431,23 +3321,13 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR17" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr"/>
       <c r="AT17" t="n">
         <v>0</v>
       </c>
-      <c r="AU17" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV17" t="inlineStr">
         <is>
           <t>nidss_open_data</t>
@@ -3567,11 +3447,6 @@
       <c r="R18" t="n">
         <v>0.04412259560257887</v>
       </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3584,23 +3459,13 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR18" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr"/>
       <c r="AT18" t="n">
         <v>0</v>
       </c>
-      <c r="AU18" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV18" t="inlineStr">
         <is>
           <t>nidss_open_data</t>
@@ -3720,11 +3585,6 @@
       <c r="R19" t="n">
         <v>0.02647355736154732</v>
       </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3737,23 +3597,13 @@
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR19" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr"/>
       <c r="AT19" t="n">
         <v>0</v>
       </c>
-      <c r="AU19" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV19" t="inlineStr">
         <is>
           <t>nidss_open_data</t>
@@ -4266,11 +4116,6 @@
       <c r="R22" t="n">
         <v>0.02198243682434508</v>
       </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4283,23 +4128,13 @@
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR22" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr"/>
       <c r="AT22" t="n">
         <v>0</v>
       </c>
-      <c r="AU22" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV22" t="inlineStr">
         <is>
           <t>nidss_open_data</t>
@@ -4419,11 +4254,6 @@
       <c r="R23" t="n">
         <v>0.0307754115540831</v>
       </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4436,23 +4266,13 @@
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR23" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr"/>
       <c r="AT23" t="n">
         <v>0</v>
       </c>
-      <c r="AU23" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV23" t="inlineStr">
         <is>
           <t>nidss_open_data</t>
@@ -4572,11 +4392,6 @@
       <c r="R24" t="n">
         <v>0.02198243682434508</v>
       </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4589,23 +4404,13 @@
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR24" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr"/>
       <c r="AT24" t="n">
         <v>0</v>
       </c>
-      <c r="AU24" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV24" t="inlineStr">
         <is>
           <t>nidss_open_data</t>
@@ -4725,11 +4530,6 @@
       <c r="R25" t="n">
         <v>0.02637892418921409</v>
       </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4742,23 +4542,13 @@
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR25" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr"/>
       <c r="AT25" t="n">
         <v>0</v>
       </c>
-      <c r="AU25" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV25" t="inlineStr">
         <is>
           <t>nidss_open_data</t>
@@ -4878,11 +4668,6 @@
       <c r="R26" t="n">
         <v>0.02637892418921409</v>
       </c>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4895,23 +4680,13 @@
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR26" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr"/>
       <c r="AT26" t="n">
         <v>0</v>
       </c>
-      <c r="AU26" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV26" t="inlineStr">
         <is>
           <t>nidss_open_data</t>
@@ -5031,11 +4806,6 @@
       <c r="R27" t="n">
         <v>0.02198243682434508</v>
       </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5048,23 +4818,13 @@
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR27" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr"/>
       <c r="AT27" t="n">
         <v>0</v>
       </c>
-      <c r="AU27" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV27" t="inlineStr">
         <is>
           <t>nidss_open_data</t>
@@ -5184,11 +4944,6 @@
       <c r="R28" t="n">
         <v>0.008792974729738031</v>
       </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5201,23 +4956,13 @@
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR28" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr"/>
       <c r="AT28" t="n">
         <v>0</v>
       </c>
-      <c r="AU28" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV28" t="inlineStr">
         <is>
           <t>nidss_open_data</t>
@@ -5337,11 +5082,6 @@
       <c r="R29" t="n">
         <v>0.04396487364869015</v>
       </c>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5354,23 +5094,13 @@
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR29" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS29" t="inlineStr"/>
       <c r="AT29" t="n">
         <v>0</v>
       </c>
-      <c r="AU29" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV29" t="inlineStr">
         <is>
           <t>nidss_open_data</t>
@@ -5490,11 +5220,6 @@
       <c r="R30" t="n">
         <v>0.02198243682434508</v>
       </c>
-      <c r="S30" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5507,23 +5232,13 @@
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR30" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS30" t="inlineStr"/>
       <c r="AT30" t="n">
         <v>0</v>
       </c>
-      <c r="AU30" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV30" t="inlineStr">
         <is>
           <t>nidss_open_data</t>
@@ -5643,11 +5358,6 @@
       <c r="R31" t="n">
         <v>0.01758594945947606</v>
       </c>
-      <c r="S31" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5660,23 +5370,13 @@
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR31" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS31" t="inlineStr"/>
       <c r="AT31" t="n">
         <v>0</v>
       </c>
-      <c r="AU31" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV31" t="inlineStr">
         <is>
           <t>nidss_open_data</t>
@@ -5796,11 +5496,6 @@
       <c r="R32" t="n">
         <v>0.02637892418921409</v>
       </c>
-      <c r="S32" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5813,23 +5508,13 @@
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR32" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS32" t="inlineStr"/>
       <c r="AT32" t="n">
         <v>0</v>
       </c>
-      <c r="AU32" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV32" t="inlineStr">
         <is>
           <t>nidss_open_data</t>
@@ -5949,11 +5634,6 @@
       <c r="R33" t="n">
         <v>0.004396487364869015</v>
       </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5966,22 +5646,12 @@
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR33" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS33" t="inlineStr"/>
       <c r="AT33" t="n">
         <v>0</v>
-      </c>
-      <c r="AU33" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV33" t="inlineStr">
         <is>
